--- a/Data/RemapDrafts/KeqingRemapDraft.xlsx
+++ b/Data/RemapDrafts/KeqingRemapDraft.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Computer\Games\Genshin\Repos\Repos\Fix-Raiden-Boss\Data\RemapDrafts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF20805-BCFC-4605-B458-3F309F5AACFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E976682-BD82-4E2E-86C7-34F28CE58CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{7DEBADF7-A4B8-4729-A1B3-FCCE2A5EC46C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="1" xr2:uid="{7DEBADF7-A4B8-4729-A1B3-FCCE2A5EC46C}"/>
   </bookViews>
   <sheets>
-    <sheet name="V4.0 -Keqing to KeqingOpulent" sheetId="1" r:id="rId1"/>
+    <sheet name="Credits" sheetId="2" r:id="rId1"/>
+    <sheet name="V4.0 -Keqing to KeqingOpulent" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V4.0 -Keqing to KeqingOpulent'!$A$1:$D$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.0 -Keqing to KeqingOpulent'!$A$1:$D$111</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>Keqing</t>
   </si>
@@ -79,12 +80,21 @@
   <si>
     <t>Feather decoration on Keqing's left thigh, I don't think there is a corresponding index  (update: for stability, this should map to some index )</t>
   </si>
+  <si>
+    <t>Authors</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>AlbertGold#2696</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,6 +105,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -118,17 +144,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -471,17 +501,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89CEFA8F-64DD-440D-8527-56BA35AF523E}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="26" x14ac:dyDescent="0.6">
+      <c r="A1" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{6ADFACB0-2EB3-4380-9215-9A77F5625AB1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{199F2C85-7A88-4940-B305-7A5E71997FD4}">
   <dimension ref="A1:D111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="68.7109375" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="68.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -495,7 +556,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -505,7 +566,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -515,7 +576,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -525,7 +586,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -537,7 +598,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -547,7 +608,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -557,7 +618,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -567,7 +628,7 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -577,7 +638,7 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -587,7 +648,7 @@
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -597,7 +658,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -607,7 +668,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -617,7 +678,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -627,7 +688,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -637,7 +698,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -647,7 +708,7 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -657,7 +718,7 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -667,7 +728,7 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -677,7 +738,7 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -687,7 +748,7 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -697,7 +758,7 @@
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -707,7 +768,7 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -719,7 +780,7 @@
       </c>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -731,7 +792,7 @@
       </c>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -741,7 +802,7 @@
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -753,7 +814,7 @@
       </c>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -765,7 +826,7 @@
       </c>
       <c r="D27" s="1"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -775,7 +836,7 @@
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -785,7 +846,7 @@
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -795,7 +856,7 @@
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -805,7 +866,7 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -815,7 +876,7 @@
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -825,7 +886,7 @@
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -835,7 +896,7 @@
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -845,7 +906,7 @@
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -855,7 +916,7 @@
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -865,7 +926,7 @@
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -875,7 +936,7 @@
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -885,7 +946,7 @@
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -895,7 +956,7 @@
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -909,7 +970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -923,7 +984,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -935,7 +996,7 @@
       </c>
       <c r="D43" s="1"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -945,7 +1006,7 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -955,7 +1016,7 @@
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -965,7 +1026,7 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
     </row>
-    <row r="47" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -977,7 +1038,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -989,7 +1050,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -999,7 +1060,7 @@
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -1011,7 +1072,7 @@
       </c>
       <c r="D50" s="1"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -1021,7 +1082,7 @@
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -1031,7 +1092,7 @@
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -1041,7 +1102,7 @@
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -1051,7 +1112,7 @@
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -1061,7 +1122,7 @@
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -1071,7 +1132,7 @@
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -1081,7 +1142,7 @@
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -1091,7 +1152,7 @@
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -1101,7 +1162,7 @@
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -1111,7 +1172,7 @@
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -1121,7 +1182,7 @@
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -1131,7 +1192,7 @@
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -1141,7 +1202,7 @@
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -1151,7 +1212,7 @@
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -1161,7 +1222,7 @@
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -1171,7 +1232,7 @@
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -1185,7 +1246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -1197,7 +1258,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -1209,7 +1270,7 @@
       </c>
       <c r="D69" s="1"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -1219,7 +1280,7 @@
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -1229,7 +1290,7 @@
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -1239,7 +1300,7 @@
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
     </row>
-    <row r="73" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -1251,7 +1312,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -1263,7 +1324,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -1273,7 +1334,7 @@
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -1283,7 +1344,7 @@
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -1295,7 +1356,7 @@
       </c>
       <c r="D77" s="1"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -1307,7 +1368,7 @@
       </c>
       <c r="D78" s="1"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -1319,7 +1380,7 @@
       </c>
       <c r="D79" s="1"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -1329,7 +1390,7 @@
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -1339,7 +1400,7 @@
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -1351,7 +1412,7 @@
       </c>
       <c r="D82" s="1"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -1361,7 +1422,7 @@
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -1371,7 +1432,7 @@
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -1381,7 +1442,7 @@
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -1391,7 +1452,7 @@
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -1401,7 +1462,7 @@
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -1411,7 +1472,7 @@
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -1421,7 +1482,7 @@
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -1431,7 +1492,7 @@
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -1441,7 +1502,7 @@
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -1453,7 +1514,7 @@
       </c>
       <c r="D92" s="1"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -1463,7 +1524,7 @@
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -1473,7 +1534,7 @@
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -1485,7 +1546,7 @@
       </c>
       <c r="D95" s="1"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -1495,7 +1556,7 @@
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -1505,7 +1566,7 @@
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
     </row>
-    <row r="98" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -1515,7 +1576,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -1525,7 +1586,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -1535,7 +1596,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -1545,7 +1606,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -1555,7 +1616,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -1565,7 +1626,7 @@
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -1575,7 +1636,7 @@
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -1587,7 +1648,7 @@
       </c>
       <c r="D105" s="1"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -1597,7 +1658,7 @@
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -1607,7 +1668,7 @@
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -1617,7 +1678,7 @@
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -1627,7 +1688,7 @@
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -1637,7 +1698,7 @@
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>109</v>
       </c>
